--- a/tests/bolts/res/M12_bolt.xlsx
+++ b/tests/bolts/res/M12_bolt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA\laghida\Documents\GitLab\cassy\tests\bolts\res\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\cassy\tests\bolts\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81D5AB07-7B05-4809-AFD4-5E13714268A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64321AB4-2443-4C91-87C0-1EAF4132E046}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{F09436F1-1F29-42A5-B1F9-53A78950820F}"/>
+    <workbookView xWindow="33735" yWindow="3405" windowWidth="21600" windowHeight="13020" xr2:uid="{F09436F1-1F29-42A5-B1F9-53A78950820F}"/>
   </bookViews>
   <sheets>
     <sheet name="Bolt Data" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="44">
   <si>
     <t>Dimensions of the bolts and assembled parts</t>
   </si>
@@ -247,6 +247,12 @@
   </si>
   <si>
     <t>material</t>
+  </si>
+  <si>
+    <t>d_vh</t>
+  </si>
+  <si>
+    <t>Venting hole diameter</t>
   </si>
 </sst>
 </file>
@@ -337,7 +343,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -640,11 +646,53 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="dotted">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color indexed="64"/>
+      </left>
+      <right style="dotted">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -740,6 +788,18 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="5" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="3" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -818,13 +878,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>107008</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>34685</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>168954</xdr:colOff>
-      <xdr:row>25</xdr:row>
+      <xdr:row>26</xdr:row>
       <xdr:rowOff>117461</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -862,13 +922,13 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>678181</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>125730</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>24</xdr:col>
       <xdr:colOff>207186</xdr:colOff>
-      <xdr:row>59</xdr:row>
+      <xdr:row>60</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -906,13 +966,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>1</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>510541</xdr:colOff>
-      <xdr:row>59</xdr:row>
+      <xdr:row>60</xdr:row>
       <xdr:rowOff>156101</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1246,23 +1306,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9A35CF97-1329-4AF8-AE95-32CC01118615}">
-  <dimension ref="A1:K24"/>
-  <sheetFormatPr defaultColWidth="8.84375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.53515625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="12.5703125" style="2" customWidth="1"/>
     <col min="2" max="2" width="44" style="2" customWidth="1"/>
-    <col min="3" max="3" width="26.69140625" style="2" customWidth="1"/>
-    <col min="4" max="11" width="11.15234375" style="2" customWidth="1"/>
-    <col min="12" max="16384" width="8.84375" style="2"/>
+    <col min="3" max="3" width="26.7109375" style="2" customWidth="1"/>
+    <col min="4" max="11" width="11.140625" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="33" t="s">
+    <row r="1" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="35"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="39"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -1271,7 +1331,7 @@
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
     </row>
-    <row r="2" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
@@ -1292,7 +1352,7 @@
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
         <v>5</v>
       </c>
@@ -1313,7 +1373,7 @@
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>8</v>
       </c>
@@ -1334,7 +1394,7 @@
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
     </row>
-    <row r="5" spans="1:11" ht="16.75" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>10</v>
       </c>
@@ -1355,7 +1415,7 @@
       <c r="J5" s="1"/>
       <c r="K5" s="1"/>
     </row>
-    <row r="6" spans="1:11" ht="16.75" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>12</v>
       </c>
@@ -1377,7 +1437,7 @@
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
     </row>
-    <row r="7" spans="1:11" ht="16.75" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>14</v>
       </c>
@@ -1398,7 +1458,7 @@
       <c r="J7" s="1"/>
       <c r="K7" s="1"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>16</v>
       </c>
@@ -1419,7 +1479,7 @@
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
     </row>
-    <row r="9" spans="1:11" ht="16.75" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>18</v>
       </c>
@@ -1441,7 +1501,7 @@
       <c r="J9" s="1"/>
       <c r="K9" s="1"/>
     </row>
-    <row r="10" spans="1:11" ht="16.75" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>36</v>
       </c>
@@ -1462,7 +1522,7 @@
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
     </row>
-    <row r="11" spans="1:11" ht="16.75" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>20</v>
       </c>
@@ -1483,17 +1543,17 @@
       <c r="J11" s="1"/>
       <c r="K11" s="1"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C12" s="31">
-        <v>6</v>
-      </c>
-      <c r="D12" s="5" t="s">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="33" t="s">
+        <v>42</v>
+      </c>
+      <c r="B12" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="35">
+        <v>0</v>
+      </c>
+      <c r="D12" s="36" t="s">
         <v>7</v>
       </c>
       <c r="E12" s="1"/>
@@ -1504,15 +1564,15 @@
       <c r="J12" s="1"/>
       <c r="K12" s="1"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C13" s="31">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>7</v>
@@ -1525,17 +1585,17 @@
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A14" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>27</v>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>25</v>
       </c>
       <c r="C14" s="31">
-        <v>0</v>
-      </c>
-      <c r="D14" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="5" t="s">
         <v>7</v>
       </c>
       <c r="E14" s="1"/>
@@ -1546,17 +1606,17 @@
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
     </row>
-    <row r="15" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A15" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="B15" s="25" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" s="32">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="31">
         <v>0</v>
       </c>
-      <c r="D15" s="23" t="s">
+      <c r="D15" s="9" t="s">
         <v>7</v>
       </c>
       <c r="E15" s="1"/>
@@ -1567,18 +1627,18 @@
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
     </row>
-    <row r="16" spans="1:11" ht="16.75" x14ac:dyDescent="0.4">
-      <c r="A16" s="26" t="s">
-        <v>28</v>
-      </c>
-      <c r="B16" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="C16" s="16">
-        <v>4</v>
-      </c>
-      <c r="D16" s="28" t="s">
-        <v>29</v>
+    <row r="16" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="C16" s="32">
+        <v>0</v>
+      </c>
+      <c r="D16" s="23" t="s">
+        <v>7</v>
       </c>
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
@@ -1588,17 +1648,17 @@
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A17" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" s="18">
-        <v>0.15</v>
-      </c>
-      <c r="D17" s="5" t="s">
+    <row r="17" spans="1:11" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="A17" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B17" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="16">
+        <v>4</v>
+      </c>
+      <c r="D17" s="28" t="s">
         <v>29</v>
       </c>
       <c r="E17" s="1"/>
@@ -1609,17 +1669,17 @@
       <c r="J17" s="1"/>
       <c r="K17" s="1"/>
     </row>
-    <row r="18" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A18" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="B18" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="C18" s="21">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="18">
         <v>0.15</v>
       </c>
-      <c r="D18" s="22" t="s">
+      <c r="D18" s="5" t="s">
         <v>29</v>
       </c>
       <c r="E18" s="1"/>
@@ -1630,15 +1690,15 @@
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
     </row>
-    <row r="19" spans="1:11" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="19" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="C19" s="21" t="s">
-        <v>39</v>
+        <v>32</v>
+      </c>
+      <c r="C19" s="21">
+        <v>0.15</v>
       </c>
       <c r="D19" s="22" t="s">
         <v>29</v>
@@ -1651,11 +1711,19 @@
       <c r="J19" s="1"/>
       <c r="K19" s="1"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.4">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
+    <row r="20" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="D20" s="22" t="s">
+        <v>29</v>
+      </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
@@ -1664,7 +1732,7 @@
       <c r="J20" s="1"/>
       <c r="K20" s="1"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
@@ -1677,7 +1745,7 @@
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
@@ -1690,7 +1758,7 @@
       <c r="J22" s="1"/>
       <c r="K22" s="1"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
@@ -1703,7 +1771,7 @@
       <c r="J23" s="1"/>
       <c r="K23" s="1"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
@@ -1715,6 +1783,19 @@
       <c r="I24" s="1"/>
       <c r="J24" s="1"/>
       <c r="K24" s="1"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
